--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>doi</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>research_area</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,6 +520,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,6 +561,11 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +602,11 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,6 +647,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +692,11 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -707,6 +737,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -747,6 +782,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -787,6 +827,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>model-serving-and-inference</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -827,6 +872,11 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -867,6 +917,11 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>model-serving-and-inference</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -907,6 +962,11 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -947,6 +1007,11 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -987,6 +1052,11 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1031,6 +1101,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1075,6 +1150,11 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1119,6 +1199,11 @@
           <t>https://doi.org/10.1145/3664647.3681426</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1159,6 +1244,11 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1199,6 +1289,11 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1245,6 +1340,11 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3643832.3661888</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>edge-and-on-device-ml</t>
         </is>
       </c>
     </row>
@@ -1287,6 +1387,11 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>model-serving-and-inference</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1335,6 +1440,11 @@
           <t>https://doi.org/10.1145/3627703.3650074</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>model-serving-and-inference</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1383,6 +1493,11 @@
           <t>https://doi.org/10.1145/3617232.3624849</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>model-serving-and-inference</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1427,6 +1542,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1471,6 +1591,11 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1511,6 +1636,11 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1551,6 +1681,11 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1591,6 +1726,11 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1635,6 +1775,11 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1675,6 +1820,11 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1715,6 +1865,11 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1759,6 +1914,11 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1799,6 +1959,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1847,6 +2012,11 @@
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1887,6 +2057,11 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1931,6 +2106,11 @@
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1975,6 +2155,11 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2015,6 +2200,11 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ai-for-systems</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2055,6 +2245,11 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>model-serving-and-inference</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2095,6 +2290,11 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2135,6 +2335,11 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2175,6 +2380,11 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2215,6 +2425,11 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>edge-and-on-device-ml</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2251,6 +2466,11 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2291,6 +2511,11 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ai-for-systems</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2331,6 +2556,11 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ai-for-systems</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2371,6 +2601,11 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ai-for-systems</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2411,6 +2646,11 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2451,6 +2691,11 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2491,6 +2736,11 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2531,6 +2781,11 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2571,6 +2826,11 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2611,6 +2871,11 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2651,6 +2916,11 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2691,6 +2961,11 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2731,6 +3006,11 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ai-for-systems</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2771,6 +3051,11 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2811,6 +3096,56 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>miscellaneous</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Zhenning Yang, Hui Guan, Victor Nicolet, Brandon Paulsen, Joey Dodds, Daniel Kroening, Ang Chen</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Automated Cloud Infrastructure-as-Code Reconciliation with AI Agents</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>arXiv, 2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>arxiv25-iac-reconciliation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2510.20211</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>arXiv'25</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>agentic-systems</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3147,6 +3147,51 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hanmei Yang, Jin Zhou, Yao Fu, Xiaoquan Wang, Ramine Roane, Hui Guan, Tongping Liu</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ProTrain: Efficient LLM Training via Automatic Memory Management</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The 9th Annual Conference on Machine Learning and Systems (MLSys 2026), Bellevue, WA, May 18-22, 2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>mlsys26-protrain-efficient</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2406.08334</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>MLSys'26</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>learning-algorithms-and-systems</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -511,15 +511,11 @@
           <t>sensys26-wildfit-autonomous</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>SenSys'26</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
@@ -552,15 +548,11 @@
           <t>pacificvis26-fourstage-framework</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>PacificVis'26</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -593,15 +585,11 @@
           <t>mmsys26-atom-efficient</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>MMSys'26</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>edge-and-on-device-ml</t>
@@ -644,9 +632,6 @@
           <t>VLDB'25</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -689,9 +674,6 @@
           <t>EXAIT@ICML'25</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -734,9 +716,6 @@
           <t>Neurocomputing@25</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -779,9 +758,6 @@
           <t>ARITH'25</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -824,9 +800,6 @@
           <t>TKDD'25</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>model-serving-and-inference</t>
@@ -869,9 +842,6 @@
           <t>MLSys'25</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -914,9 +884,6 @@
           <t>MLSys'25</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>model-serving-and-inference</t>
@@ -959,9 +926,6 @@
           <t>CHI EA'25</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -1004,9 +968,6 @@
           <t>MLforSys@NeurIPS'24</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1049,9 +1010,6 @@
           <t>AI4Mat@NeurIPS'24</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1099,8 +1057,6 @@
           <t>https://github.com/zhanglijun95/ZoDiac</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1148,8 +1104,6 @@
           <t>https://github.com/Astuary/Spry</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
@@ -1192,8 +1146,6 @@
           <t>ACM MM'24</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3664647.3681426</t>
@@ -1241,9 +1193,6 @@
           <t>MIPR'24</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1286,9 +1235,6 @@
           <t>IEEE Access'24</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1336,7 +1282,6 @@
           <t>https://github.com/mmehdirk/CACTUS-Dynamically-Switchable-Context-aware-micro-Classifiers-for-Efficient-IoT-Inference</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3643832.3661888</t>
@@ -1384,9 +1329,6 @@
           <t>HPDC'24</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>model-serving-and-inference</t>
@@ -1434,7 +1376,6 @@
           <t>https://github.com/qizhengyang98/GMorph/tree/master</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3627703.3650074</t>
@@ -1487,7 +1428,6 @@
           <t>https://github.com/UMass-LIDS/Proteus</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3617232.3624849</t>
@@ -1540,8 +1480,6 @@
           <t>https://github.com/Astuary/Flow</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
@@ -1589,8 +1527,6 @@
           <t>https://zenodo.org/record/8350579</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -1633,9 +1569,6 @@
           <t>MobiCom'23</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>edge-and-on-device-ml</t>
@@ -1678,9 +1611,6 @@
           <t>ICML'23</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
@@ -1723,9 +1653,6 @@
           <t>ICML'23</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -1773,8 +1700,6 @@
           <t>https://github.com/zhanglijun95/TreeMTL</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1817,9 +1742,6 @@
           <t>ISMM'23</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -1862,9 +1784,6 @@
           <t>IEEE Access'23</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1912,8 +1831,6 @@
           <t>https://github.com/zhanglijun95/AutoMTL</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -1956,9 +1873,6 @@
           <t>VLDB'22</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2011,7 +1925,6 @@
           <t>Teaser~&gt;https://www.youtube.com/watch?v=t9r474WdBEQ|Video~&gt;https://www.youtube.com/watch?v=DobkdkBMFrg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2054,9 +1967,6 @@
           <t>ICME'22</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2099,13 +2009,11 @@
           <t>AI4Science@ICML'22</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>talk~&gt;https://slideslive.com/38986179/improving-subgraph-representation-learning-via-multiview-augmentation</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2148,13 +2056,11 @@
           <t>CrossFL'22</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Poster~&gt;https://crossfl2022.github.io/posters/Poster9.pdf</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems,edge-and-on-device-ml</t>
@@ -2197,9 +2103,6 @@
           <t>CGO'22</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>ai-for-systems</t>
@@ -2242,9 +2145,6 @@
           <t>ICDM'21</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>model-serving-and-inference</t>
@@ -2287,9 +2187,6 @@
           <t>OSR'21</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2332,9 +2229,6 @@
           <t>ICS'21</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -2377,9 +2271,6 @@
           <t>MCHPC'21</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2422,9 +2313,6 @@
           <t>CACM'21</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>edge-and-on-device-ml</t>
@@ -2457,15 +2345,11 @@
           <t>2021kmeans</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>InformationSystems'21</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2508,9 +2392,6 @@
           <t>CC'21</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>ai-for-systems</t>
@@ -2553,9 +2434,6 @@
           <t>FSE'20</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>ai-for-systems</t>
@@ -2598,9 +2476,6 @@
           <t>TPDS'20</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>ai-for-systems</t>
@@ -2643,9 +2518,6 @@
           <t>MLSys'20</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2688,9 +2560,6 @@
           <t>NeurIPS'19</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2733,9 +2602,6 @@
           <t>MLSys@NeurIPS'19</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2778,9 +2644,6 @@
           <t>PLDI'19</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2823,9 +2686,6 @@
           <t>ICDE'19</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2868,9 +2728,6 @@
           <t>SC'18</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2913,9 +2770,6 @@
           <t>ICDE'18</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -2948,19 +2802,11 @@
           <t>2018top</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>http://guanh01.github.io/files/2018top.pdf</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>SysML'18</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -3003,9 +2849,6 @@
           <t>SC'17</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>ai-for-systems</t>
@@ -3048,9 +2891,6 @@
           <t>PLDI'17</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>
@@ -3093,9 +2933,6 @@
           <t>SPAWC'16</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>miscellaneous</t>
@@ -3138,9 +2975,6 @@
           <t>arXiv'25</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>agentic-systems</t>
@@ -3183,9 +3017,6 @@
           <t>MLSys'26</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>learning-algorithms-and-systems</t>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huiguan/Documents/projects/website/guanh01.github.io/markdown_generator/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15BF59C-E369-D14C-9663-B6A6BF281763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="435">
   <si>
     <t>pub_date</t>
   </si>
@@ -1317,13 +1323,16 @@
   </si>
   <si>
     <t>agentic-systems</t>
+  </si>
+  <si>
+    <t>https://github.com/Astuary/Gradient_Estimation_Methods</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1399,13 +1408,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1443,7 +1460,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1477,6 +1494,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1511,9 +1529,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1686,11 +1705,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1725,7 +1747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1751,7 +1773,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1777,7 +1799,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1803,7 +1825,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1826,7 +1848,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1852,7 +1874,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1878,7 +1900,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1904,7 +1926,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1930,7 +1952,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1956,7 +1978,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1982,7 +2004,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2008,7 +2030,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2034,7 +2056,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2060,7 +2082,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2086,7 +2108,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2112,7 +2134,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2138,7 +2160,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2164,7 +2186,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2190,7 +2212,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2216,7 +2238,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2242,7 +2264,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2268,7 +2290,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2297,7 +2319,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -2329,7 +2351,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -2355,7 +2377,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -2384,7 +2406,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -2410,7 +2432,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -2439,7 +2461,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -2468,7 +2490,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -2494,7 +2516,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2520,7 +2542,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -2546,7 +2568,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2572,7 +2594,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2601,7 +2623,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2627,7 +2649,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2656,7 +2678,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2688,7 +2710,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2720,7 +2742,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2746,7 +2768,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -2778,7 +2800,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -2804,7 +2826,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -2830,7 +2852,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -2859,7 +2881,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -2885,7 +2907,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -2911,7 +2933,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -2940,7 +2962,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -2969,7 +2991,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -2995,7 +3017,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>41</v>
       </c>
@@ -3021,7 +3043,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -3047,7 +3069,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>42</v>
       </c>
@@ -3073,7 +3095,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>42</v>
       </c>
@@ -3099,7 +3121,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -3125,7 +3147,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -3151,7 +3173,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -3177,7 +3199,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -3203,7 +3225,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -3229,7 +3251,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -3252,7 +3274,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -3278,7 +3300,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -3304,7 +3326,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>49</v>
       </c>
@@ -3330,7 +3352,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -3356,7 +3378,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>50</v>
       </c>
@@ -3378,11 +3400,14 @@
       <c r="G63" t="s">
         <v>410</v>
       </c>
+      <c r="H63" s="2" t="s">
+        <v>434</v>
+      </c>
       <c r="K63" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -3410,81 +3435,82 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F6" r:id="rId4"/>
-    <hyperlink ref="F7" r:id="rId5"/>
-    <hyperlink ref="F8" r:id="rId6"/>
-    <hyperlink ref="F9" r:id="rId7"/>
-    <hyperlink ref="F10" r:id="rId8"/>
-    <hyperlink ref="F11" r:id="rId9"/>
-    <hyperlink ref="F12" r:id="rId10"/>
-    <hyperlink ref="F13" r:id="rId11"/>
-    <hyperlink ref="F14" r:id="rId12"/>
-    <hyperlink ref="F15" r:id="rId13"/>
-    <hyperlink ref="F16" r:id="rId14"/>
-    <hyperlink ref="F17" r:id="rId15"/>
-    <hyperlink ref="F18" r:id="rId16"/>
-    <hyperlink ref="F19" r:id="rId17"/>
-    <hyperlink ref="F20" r:id="rId18"/>
-    <hyperlink ref="F21" r:id="rId19"/>
-    <hyperlink ref="F22" r:id="rId20"/>
-    <hyperlink ref="F23" r:id="rId21"/>
-    <hyperlink ref="F24" r:id="rId22"/>
-    <hyperlink ref="H24" r:id="rId23"/>
-    <hyperlink ref="F25" r:id="rId24"/>
-    <hyperlink ref="F26" r:id="rId25"/>
-    <hyperlink ref="F27" r:id="rId26"/>
-    <hyperlink ref="F28" r:id="rId27"/>
-    <hyperlink ref="H28" r:id="rId28"/>
-    <hyperlink ref="F29" r:id="rId29"/>
-    <hyperlink ref="H29" r:id="rId30"/>
-    <hyperlink ref="F30" r:id="rId31"/>
-    <hyperlink ref="F31" r:id="rId32"/>
-    <hyperlink ref="F32" r:id="rId33"/>
-    <hyperlink ref="F33" r:id="rId34"/>
-    <hyperlink ref="F34" r:id="rId35"/>
-    <hyperlink ref="H34" r:id="rId36"/>
-    <hyperlink ref="F35" r:id="rId37"/>
-    <hyperlink ref="F36" r:id="rId38"/>
-    <hyperlink ref="H36" r:id="rId39"/>
-    <hyperlink ref="F37" r:id="rId40"/>
-    <hyperlink ref="H37" r:id="rId41"/>
-    <hyperlink ref="J37" r:id="rId42"/>
-    <hyperlink ref="F38" r:id="rId43"/>
-    <hyperlink ref="H38" r:id="rId44"/>
-    <hyperlink ref="J38" r:id="rId45"/>
-    <hyperlink ref="F39" r:id="rId46"/>
-    <hyperlink ref="F40" r:id="rId47"/>
-    <hyperlink ref="H40" r:id="rId48"/>
-    <hyperlink ref="J40" r:id="rId49"/>
-    <hyperlink ref="F41" r:id="rId50"/>
-    <hyperlink ref="F42" r:id="rId51"/>
-    <hyperlink ref="F43" r:id="rId52"/>
-    <hyperlink ref="J43" r:id="rId53"/>
-    <hyperlink ref="F44" r:id="rId54"/>
-    <hyperlink ref="F45" r:id="rId55"/>
-    <hyperlink ref="F46" r:id="rId56"/>
-    <hyperlink ref="H46" r:id="rId57"/>
-    <hyperlink ref="F47" r:id="rId58"/>
-    <hyperlink ref="H47" r:id="rId59"/>
-    <hyperlink ref="F48" r:id="rId60"/>
-    <hyperlink ref="F49" r:id="rId61"/>
-    <hyperlink ref="F50" r:id="rId62"/>
-    <hyperlink ref="F51" r:id="rId63"/>
-    <hyperlink ref="F52" r:id="rId64"/>
-    <hyperlink ref="F53" r:id="rId65"/>
-    <hyperlink ref="F54" r:id="rId66"/>
-    <hyperlink ref="F55" r:id="rId67"/>
-    <hyperlink ref="F56" r:id="rId68"/>
-    <hyperlink ref="F57" r:id="rId69"/>
-    <hyperlink ref="F59" r:id="rId70"/>
-    <hyperlink ref="F60" r:id="rId71"/>
-    <hyperlink ref="F61" r:id="rId72"/>
-    <hyperlink ref="F62" r:id="rId73"/>
-    <hyperlink ref="F63" r:id="rId74"/>
-    <hyperlink ref="F64" r:id="rId75"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="H24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="H28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="H29" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F30" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F31" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F32" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F33" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="H34" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F35" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F36" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="H36" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F37" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="H37" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="J37" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F38" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="H38" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="J38" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F39" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F40" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="H40" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="J40" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F41" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F42" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F43" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="J43" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F44" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F45" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F46" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="H46" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F47" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="H47" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F48" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F49" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F50" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F51" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F52" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F53" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F54" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F55" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F56" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F57" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F59" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F60" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F61" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F62" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F63" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F64" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="H63" r:id="rId76" xr:uid="{89D19EAB-1DF0-B44A-9A08-ED94402A2C41}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
